--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/12,10,26 Останкино КИ и ЗПФ/дв 12,10,26 бррсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/12,10,26 Останкино КИ и ЗПФ/дв 12,10,26 бррсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\12,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2446A34-68DD-45EF-88C6-22E1CE2F96C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04391043-4FF5-4F22-9D00-39020141EE8B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="179">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -588,6 +588,9 @@
   <si>
     <t>20,10,</t>
   </si>
+  <si>
+    <t>увеличить / матрица</t>
+  </si>
 </sst>
 </file>
 
@@ -647,7 +650,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -688,6 +691,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -724,7 +733,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -748,6 +757,7 @@
     <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -5494,7 +5504,8 @@
     <col min="22" max="31" width="6" customWidth="1"/>
     <col min="32" max="32" width="48.28515625" customWidth="1"/>
     <col min="33" max="33" width="7" customWidth="1"/>
-    <col min="34" max="50" width="3" customWidth="1"/>
+    <col min="34" max="34" width="8.140625" customWidth="1"/>
+    <col min="35" max="50" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.25">
@@ -6078,7 +6089,7 @@
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5">
-        <f t="shared" ref="R7:R70" si="5">ROUND(Q7,0)</f>
+        <f t="shared" ref="R7:R69" si="5">ROUND(Q7,0)</f>
         <v>0</v>
       </c>
       <c r="S7" s="21"/>
@@ -6377,7 +6388,7 @@
       <c r="AX9" s="1"/>
     </row>
     <row r="10" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="23" t="s">
         <v>44</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -9462,7 +9473,7 @@
       <c r="AX36" s="1"/>
     </row>
     <row r="37" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="23" t="s">
         <v>79</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -10955,7 +10966,7 @@
       <c r="AX49" s="1"/>
     </row>
     <row r="50" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="23" t="s">
         <v>96</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -11182,7 +11193,7 @@
       <c r="AX51" s="1"/>
     </row>
     <row r="52" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="23" t="s">
         <v>99</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -12542,7 +12553,10 @@
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AH63" s="1"/>
+      <c r="AH63" s="1">
+        <f>77/5</f>
+        <v>15.4</v>
+      </c>
       <c r="AI63" s="1"/>
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
@@ -13626,7 +13640,7 @@
         <v>86</v>
       </c>
       <c r="R73" s="5">
-        <f t="shared" ref="R71:R110" si="20">ROUND(Q73,0)</f>
+        <f t="shared" ref="R73:R110" si="20">ROUND(Q73,0)</f>
         <v>86</v>
       </c>
       <c r="S73" s="21"/>
@@ -15381,7 +15395,10 @@
         <f t="shared" si="19"/>
         <v>62.400000000000006</v>
       </c>
-      <c r="AH88" s="1"/>
+      <c r="AH88" s="1">
+        <f>P88/V88</f>
+        <v>4.666666666666667</v>
+      </c>
       <c r="AI88" s="1"/>
       <c r="AJ88" s="1"/>
       <c r="AK88" s="1"/>
@@ -15891,7 +15908,7 @@
         <v>60</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>36</v>
+        <v>178</v>
       </c>
       <c r="J93" s="1"/>
       <c r="K93" s="1">
